--- a/public/member_template.xlsx
+++ b/public/member_template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>ល.រ</t>
   </si>
@@ -79,6 +79,39 @@
   </si>
   <si>
     <t>សរុបចំនួន  នាក់ (ស្រី  នាក់)</t>
+  </si>
+  <si>
+    <t>ទុំ ឡង់ឌី</t>
+  </si>
+  <si>
+    <t>TUM LONGDY</t>
+  </si>
+  <si>
+    <t>ស្រី</t>
+  </si>
+  <si>
+    <t>០៨ ធ្នូ ១៩៩៨</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>វិទ្យាល័យ ព្រៃព្នៅ</t>
+  </si>
+  <si>
+    <t>សមាជិកា យុវជន</t>
+  </si>
+  <si>
+    <t>ថ្នាក់ទី១១</t>
+  </si>
+  <si>
+    <t>២០១៤-២០១៥</t>
+  </si>
+  <si>
+    <t>ភូមិព្រៃព្នៅ ឃុំព្រៃព្នៅ ស្រុកពារាំង ខេត្តព្រៃវែង</t>
+  </si>
+  <si>
+    <t>០៧១ ៨៤៦៧ ៣២៣</t>
   </si>
 </sst>
 </file>
@@ -627,6 +660,7 @@
   <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
+    <col min="1" max="1" width="11.69140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.4609375" customWidth="1"/>
     <col min="3" max="3" width="19.3828125" customWidth="1"/>
     <col min="5" max="5" width="21.3046875" customWidth="1"/>
@@ -772,21 +806,47 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="25.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="A6" s="9">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
+      <c r="L6" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="13">
+        <v>45658</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>30</v>
+      </c>
       <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16" ht="25.3">

--- a/public/member_template.xlsx
+++ b/public/member_template.xlsx
@@ -1,25 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1997" yWindow="1063" windowWidth="15377" windowHeight="7877"/>
+    <workbookView windowWidth="24685" windowHeight="12162"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+  <si>
+    <t>កាកបាទក្រហមកម្ពុជា</t>
+  </si>
+  <si>
+    <t>សាខាខេត្ត</t>
+  </si>
+  <si>
+    <t>ទិន្នន័យគ្រឹះស្ថានសិក្សា ទីប្រឹក្សាយុវជន និងយុវជនកាកបាទក្រហមកម្ពុជា ឆ្នាំ</t>
+  </si>
   <si>
     <t>ល.រ</t>
   </si>
@@ -33,30 +50,30 @@
     <t>ភេទ</t>
   </si>
   <si>
+    <t>ថ្ងៃខែឆ្នាំកំណើត</t>
+  </si>
+  <si>
+    <t>ទីកន្លែងកំណើត</t>
+  </si>
+  <si>
+    <t>គ្រឹះស្ថានសិក្សា</t>
+  </si>
+  <si>
     <t>តួនាទី</t>
   </si>
   <si>
+    <t>កម្រិតសិក្សា</t>
+  </si>
+  <si>
+    <t>ទទួលបានវគ្គបណ្ដុះបណ្ដាល</t>
+  </si>
+  <si>
     <t>ពិការភាព</t>
   </si>
   <si>
     <t>ឆ្នាំសិក្សា</t>
   </si>
   <si>
-    <t>ទីកន្លែងកំណើត</t>
-  </si>
-  <si>
-    <t>ថ្ងៃខែឆ្នាំកំណើត</t>
-  </si>
-  <si>
-    <t>គ្រឹះស្ថានសិក្សា</t>
-  </si>
-  <si>
-    <t>កម្រិតសិក្សា</t>
-  </si>
-  <si>
-    <t>ទទួលបានវគ្គបណ្ដុះបណ្ដាល</t>
-  </si>
-  <si>
     <t>ថ្ងៃខែឆ្នាំចូលជាសមាជិក</t>
   </si>
   <si>
@@ -69,125 +86,463 @@
     <t>ទូរស័ព្ទអាណាព្យាបាល</t>
   </si>
   <si>
-    <t>កាកបាទក្រហមកម្ពុជា</t>
-  </si>
-  <si>
-    <t>សាខាខេត្ត</t>
-  </si>
-  <si>
-    <t>ទិន្នន័យគ្រឹះស្ថានសិក្សា ទីប្រឹក្សាយុវជន និងយុវជនកាកបាទក្រហមកម្ពុជា ឆ្នាំ</t>
+    <t>ទុំ ឡង់ឌី</t>
+  </si>
+  <si>
+    <t>TUM LONGDY</t>
+  </si>
+  <si>
+    <t>ស្រី</t>
+  </si>
+  <si>
+    <t>០៨ ធ្នូ ១៩៩៨</t>
+  </si>
+  <si>
+    <t>ភូមិព្រៃព្នៅ ឃុំព្រៃព្នៅ ស្រុកពារាំង ខេត្តព្រៃវែង</t>
+  </si>
+  <si>
+    <t>វិទ្យាល័យ ព្រៃព្នៅ</t>
+  </si>
+  <si>
+    <t>សមាជិកា យុវជន</t>
+  </si>
+  <si>
+    <t>ថ្នាក់ទី១១</t>
+  </si>
+  <si>
+    <t>២០១៤-២០១៥</t>
+  </si>
+  <si>
+    <t>០៧១ ៨៤៦៧ ៣២៣</t>
   </si>
   <si>
     <t>សរុបចំនួន  នាក់ (ស្រី  នាក់)</t>
-  </si>
-  <si>
-    <t>ទុំ ឡង់ឌី</t>
-  </si>
-  <si>
-    <t>TUM LONGDY</t>
-  </si>
-  <si>
-    <t>ស្រី</t>
-  </si>
-  <si>
-    <t>០៨ ធ្នូ ១៩៩៨</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>វិទ្យាល័យ ព្រៃព្នៅ</t>
-  </si>
-  <si>
-    <t>សមាជិកា យុវជន</t>
-  </si>
-  <si>
-    <t>ថ្នាក់ទី១១</t>
-  </si>
-  <si>
-    <t>២០១៤-២០១៥</t>
-  </si>
-  <si>
-    <t>ភូមិព្រៃព្នៅ ឃុំព្រៃព្នៅ ស្រុកពារាំង ខេត្តព្រៃវែង</t>
-  </si>
-  <si>
-    <t>០៧១ ៨៤៦៧ ៣២៣</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="[$-12000425]0"/>
-    <numFmt numFmtId="165" formatCode="000"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="7">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="[$-12000425]0"/>
+    <numFmt numFmtId="179" formatCode="000"/>
+    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF5A30D0"/>
+      <name val="Khmer OS Muol"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF5A30D0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Khmer OS Battambang"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Khmer OS Battambang"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Khmer OS Battambang"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="!Khmer OS Siemreap"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="!Khmer OS Siemreap"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Khmer OS Siemreap"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Khmer OS Battambang"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Khmer OS Battambang"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF5A30D0"/>
-      <name val="Khmer OS Muol"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF5A30D0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Khmer OS Battambang"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Khmer OS Battambang"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -197,16 +552,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -214,88 +569,374 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF5A30D0"/>
-      <color rgb="FF000000"/>
+      <color rgb="005A30D0"/>
+      <color rgb="00000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -311,19 +952,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7" descr="CRC LOGO_3_inch">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF2DF649-6DA6-4741-A0CC-4B6F1636CCED}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="8" name="Picture 7" descr="CRC LOGO_3_inch"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -335,10 +970,10 @@
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="12520619" y="169294"/>
-          <a:ext cx="1185129" cy="1253670"/>
+          <a:off x="16054070" y="168910"/>
+          <a:ext cx="1185545" cy="1253490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -436,23 +1071,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -488,23 +1106,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -646,218 +1247,213 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:P7"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.55" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="11.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.4609375" customWidth="1"/>
-    <col min="3" max="3" width="19.3828125" customWidth="1"/>
-    <col min="5" max="5" width="21.3046875" customWidth="1"/>
-    <col min="6" max="6" width="15.3046875" customWidth="1"/>
-    <col min="7" max="7" width="17.69140625" customWidth="1"/>
+    <col min="1" max="1" width="11.6936936936937" customWidth="1"/>
+    <col min="2" max="2" width="19.4594594594595" customWidth="1"/>
+    <col min="3" max="3" width="19.3783783783784" customWidth="1"/>
+    <col min="5" max="5" width="21.3063063063063" customWidth="1"/>
+    <col min="6" max="6" width="63.7927927927928" customWidth="1"/>
+    <col min="7" max="7" width="17.6936936936937" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="25.4609375" customWidth="1"/>
-    <col min="10" max="10" width="40.53515625" customWidth="1"/>
-    <col min="11" max="11" width="14.23046875" customWidth="1"/>
-    <col min="12" max="12" width="25.15234375" customWidth="1"/>
-    <col min="13" max="13" width="28.53515625" customWidth="1"/>
-    <col min="14" max="14" width="48.15234375" customWidth="1"/>
-    <col min="15" max="15" width="28.4609375" customWidth="1"/>
-    <col min="16" max="16" width="32.4609375" customWidth="1"/>
+    <col min="9" max="9" width="25.4594594594595" customWidth="1"/>
+    <col min="10" max="10" width="40.5315315315315" customWidth="1"/>
+    <col min="11" max="11" width="14.2342342342342" customWidth="1"/>
+    <col min="12" max="12" width="25.1531531531532" customWidth="1"/>
+    <col min="13" max="13" width="28.5315315315315" customWidth="1"/>
+    <col min="14" max="14" width="48.1531531531532" customWidth="1"/>
+    <col min="15" max="15" width="28.4594594594595" customWidth="1"/>
+    <col min="16" max="16" width="32.4594594594595" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="126.9" customHeight="1">
-      <c r="A1" s="15"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
+    <row r="1" ht="126.9" customHeight="1" spans="1:16">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="34.75">
-      <c r="A2" s="16" t="s">
+    <row r="2" ht="17.55" spans="1:16">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+    </row>
+    <row r="3" ht="17.55" spans="1:16">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" ht="17.55" spans="1:16">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" ht="22.7" spans="1:16">
+      <c r="A5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
+      <c r="O5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" s="15" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="3" spans="1:16" ht="34.75">
-      <c r="A3" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
+    <row r="6" ht="23.1" spans="1:16">
+      <c r="A6" s="6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="17">
+        <v>45658</v>
+      </c>
+      <c r="N6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="34.75">
-      <c r="A4" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-    </row>
-    <row r="5" spans="1:16" ht="25.3">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" ht="25.3">
-      <c r="A6" s="9">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" s="13">
-        <v>45658</v>
-      </c>
-      <c r="N6" s="14" t="s">
+    <row r="7" ht="15" spans="1:6">
+      <c r="A7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="8"/>
-    </row>
-    <row r="7" spans="1:16" ht="25.3">
-      <c r="A7" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -868,7 +1464,8 @@
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/member_template.xlsx
+++ b/public/member_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>កាកបាទក្រហមកម្ពុជា</t>
   </si>
@@ -123,16 +123,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="[$-12000425]0"/>
     <numFmt numFmtId="179" formatCode="000"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,13 +194,6 @@
       <sz val="11"/>
       <name val="Khmer OS Battambang"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -675,148 +667,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -864,7 +856,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1434,8 +1426,8 @@
       <c r="L6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="17">
-        <v>45658</v>
+      <c r="M6" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="N6" s="18" t="s">
         <v>23</v>
@@ -1443,7 +1435,9 @@
       <c r="O6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="P6" s="10"/>
+      <c r="P6" s="10" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="7" ht="15" spans="1:6">
       <c r="A7" s="12" t="s">
